--- a/data/input/feeders/PA217/Control_Simulacion.xlsx
+++ b/data/input/feeders/PA217/Control_Simulacion.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6038</v>
+        <v>9537.879999999999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2588</v>
+        <v>2587.65</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-20 UI</t>
+          <t>3/03/2026 10:00:00</t>
         </is>
       </c>
     </row>

--- a/data/input/feeders/PA217/Control_Simulacion.xlsx
+++ b/data/input/feeders/PA217/Control_Simulacion.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9537.879999999999</v>
+        <v>2565.9541</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2587.65</v>
+        <v>696.1496</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/data/input/feeders/PA217/Control_Simulacion.xlsx
+++ b/data/input/feeders/PA217/Control_Simulacion.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2565.9541</v>
+        <v>6493.096</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>696.1496</v>
+        <v>1761.5927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
